--- a/Design/Configs/MapElements.xlsx
+++ b/Design/Configs/MapElements.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52066CAE-C9E9-4713-A91B-45EE848D2487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="1110" yWindow="1440" windowWidth="25770" windowHeight="12915" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="29">
   <si>
     <t>ConfigId</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -126,13 +127,17 @@
   </si>
   <si>
     <t>Showa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TreasureGroupId</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -450,8 +455,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.625" customWidth="1"/>
@@ -466,9 +471,10 @@
     <col min="10" max="10" width="14.25" customWidth="1"/>
     <col min="11" max="11" width="17.75" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="19.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -505,8 +511,11 @@
       <c r="L1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -543,8 +552,11 @@
       <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -581,8 +593,11 @@
       <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -619,8 +634,11 @@
       <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -657,8 +675,11 @@
       <c r="L5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -695,8 +716,11 @@
       <c r="L6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -733,8 +757,11 @@
       <c r="L7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -771,8 +798,11 @@
       <c r="L8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -809,8 +839,11 @@
       <c r="L9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -847,8 +880,11 @@
       <c r="L10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -883,6 +919,9 @@
         <v>0</v>
       </c>
       <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
     </row>

--- a/Design/Configs/MapElements.xlsx
+++ b/Design/Configs/MapElements.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52066CAE-C9E9-4713-A91B-45EE848D2487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18066C44-4497-47FA-A248-C0B589CF8D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="1440" windowWidth="25770" windowHeight="12915" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26175" yWindow="4365" windowWidth="28830" windowHeight="15630" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -138,7 +138,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +148,15 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -174,8 +183,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -459,469 +474,470 @@
   <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.625" customWidth="1"/>
-    <col min="2" max="2" width="13.75" customWidth="1"/>
-    <col min="3" max="3" width="12.5" customWidth="1"/>
-    <col min="4" max="4" width="12.375" customWidth="1"/>
-    <col min="5" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="21.125" customWidth="1"/>
-    <col min="7" max="7" width="14.875" customWidth="1"/>
-    <col min="8" max="8" width="16.125" customWidth="1"/>
-    <col min="9" max="9" width="11.875" customWidth="1"/>
-    <col min="10" max="10" width="14.25" customWidth="1"/>
-    <col min="11" max="11" width="17.75" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="19.875" customWidth="1"/>
+    <col min="1" max="1" width="17.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="14.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="16.125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="11.875" style="2" customWidth="1"/>
+    <col min="10" max="10" width="14.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="14" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19.875" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2">
         <v>15</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>15</v>
       </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>9</v>
       </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2">
         <v>3</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>3</v>
       </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>2</v>
       </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>4</v>
       </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2">
         <v>2</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>2</v>
       </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>3</v>
       </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2">
         <v>3</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>3</v>
       </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>6</v>
       </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
+      <c r="E7" s="2">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
         <v>4</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>4</v>
       </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>8</v>
       </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2">
         <v>5</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>5</v>
       </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>8</v>
       </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
+      <c r="E9" s="2">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2">
         <v>6</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>6</v>
       </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A10">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>8</v>
       </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2">
         <v>7</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>7</v>
       </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A11">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>8</v>
       </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
+      <c r="E11" s="2">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2">
         <v>8</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>8</v>
       </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
         <v>0</v>
       </c>
     </row>
